--- a/magazine_rack.xlsx
+++ b/magazine_rack.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0ce1d52e600c3/Documents/keeping up/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/betulesairafi/Git/beetlesoup.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="8_{59210B58-2A7C-6148-A80F-A4E35A7BBED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C154580-EE04-754E-A5B6-5A864CF1CF57}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0432C0D2-DDD0-7345-9D56-4AF8419C3CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11000" yWindow="500" windowWidth="14520" windowHeight="14900" xr2:uid="{32233D0D-B109-5043-A6DB-4E443C8DF167}"/>
   </bookViews>
@@ -65,11 +65,6 @@
     <t>Category</t>
   </si>
   <si>
-    <t>In October 2019, high school students protested against a rush hour metro fare rise by leaping turnstiles in stations around Santiago, marking the beginning of three tumultuous years of protest and political upheaval. During that time, a new constitution was drafted and today, for the first time, everyone over 18 must vote.&lt;br&gt;&lt;br&gt;
-        The draft "enshrines" gender parity [umm, what?], recognizes Chile's Indigenous peoples for the first time, and makes the state responsible for mitigating climate change. It has come under fierce criticism for its shakeup of the political system. Should the proposal be rejected, the 1980-born document drawn up during Gen Augusto Pinochet's dictatorship will remain in force while a solution is sought, and Chileans will brace for more protests.&lt;br&gt;&lt;br&gt;
-        &lt;span class="quotered"&gt;"The political system [it proposes] is an experiment - there's nothing like it around the world - and the list of social rights will be difficult to fund. It's irresponsible."&lt;/span&gt;</t>
-  </si>
-  <si>
     <t>World</t>
   </si>
   <si>
@@ -170,9 +165,6 @@
     <t>Biology</t>
   </si>
   <si>
-    <t>&lt;i&gt;Staphylococcus hominins&lt;/i&gt;, one of the 200 or so bacteria on some people's skin, &lt;a class="two" href="https://www.nature.com/articles/s41598-020-68860-z"&gt;produces an onion smell&lt;/a&gt; after &lt;a class="two" href="https://youtu.be/dNBotNm7PUc"&gt;eating the sweat&lt;/a&gt; it finds on the body. It also kills MRSA(!!!) by punching holes in its cell membrane. As the water evaporates, sweat antibiotics increase in concentration. So it kind of leaves a little coating on your skin. &lt;span class="highlight"&gt;Onion-smelling sweat is antibiotic juice. Don't worry about washing it off; it's deep in your pores.&lt;/span&gt;</t>
-  </si>
-  <si>
     <t>🏺</t>
   </si>
   <si>
@@ -235,15 +227,22 @@
     <t>The Guardian</t>
   </si>
   <si>
+    <t>Opinions and Ideas</t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>In October 2019, high school students protested against a rush hour metro fare rise by leaping turnstiles in stations around Santiago, marking the beginning of three tumultuous years of protest and political upheaval. During that time, a new constitution was drafted and today, for the first time, everyone over 18 must vote.&lt;br&gt;&lt;br&gt;The draft "enshrines" gender parity [umm, what?], recognizes Chile's Indigenous peoples for the first time, and makes the state responsible for mitigating climate change. It has come under fierce criticism for its shakeup of the political system. Should the proposal be rejected, the 1980-born document drawn up during Gen Augusto Pinochet's dictatorship will remain in force while a solution is sought, and Chileans will brace for more protests.&lt;br&gt;&lt;br&gt;
+        &lt;span class="quotered"&gt;"The political system [it proposes] is an experiment - there's nothing like it around the world - and the list of social rights will be difficult to fund. It's irresponsible."&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;em&gt;Staphylococcus hominins&lt;/em&gt;, one of the 200 or so bacteria on some people's skin, &lt;a class="two" href="https://www.nature.com/articles/s41598-020-68860-z"&gt;produces an onion smell&lt;/a&gt; after &lt;a class="two" href="https://youtu.be/dNBotNm7PUc"&gt;eating the sweat&lt;/a&gt; it finds on the body. It also kills MRSA(!!!) by punching holes in its cell membrane. As the water evaporates, sweat antibiotics increase in concentration. So it kind of leaves a little coating on your skin. &lt;span class="highlight"&gt;Onion-smelling sweat is antibiotic juice. Don't worry about washing it off; it's deep in your pores.&lt;/span&gt;</t>
+  </si>
+  <si>
     <t>Although &lt;span class="highlight"&gt;AF seems to be complaining about not understanding a book whose whole thesis is that nobody actually understands each other outside of small social circles, 😛&lt;/span&gt; his scathing review of pop social science makes some valid points, such as chasing down MG's cited statistic about poets having the highest suicide rate and exposing how stupidly (ahem, uninformedly) it was calculated. There's also this gem about Truth-Default Theory, the theory that states that people are more likely to assume truth in the absence of reason to be suspicious:&lt;br&gt;&lt;br&gt;
-        &lt;span class="quotered"&gt;"I don't know whether &lt;i&gt;default to truth&lt;/i&gt; will enter the Gladwell lexicon with tipping point and stickiness. But his appropriation of the phrase does show that his attitude to social science remains unquestioning. When he encounters a study published in a journal with a complicated name, he &lt;i&gt;defaults to swallowing it whole."&lt;/i&gt;&lt;/span&gt;&lt;br&gt;
-        He ends the article praising MG for his newfound epistemological humility, which &lt;i&gt;of course, wouldn't have sold all those million books if he had begun practicing it 20 years earlier.&lt;/i&gt;</t>
-  </si>
-  <si>
-    <t>Opinions and Ideas</t>
-  </si>
-  <si>
-    <t>Books</t>
+        &lt;span class="quotered"&gt;"I don't know whether &lt;em&gt;default to truth&lt;/em&gt; will enter the Gladwell lexicon with tipping point and stickiness. But his appropriation of the phrase does show that his attitude to social science remains unquestioning. When he encounters a study published in a journal with a complicated name, he &lt;em&gt;defaults to swallowing it whole."&lt;/em&gt;&lt;/span&gt;&lt;br&gt;
+        He ends the article praising MG for his newfound epistemological humility, which &lt;em&gt;of course, wouldn't have sold all those million books if he had begun practicing it 20 years earlier.&lt;/em&gt;</t>
   </si>
 </sst>
 </file>
@@ -687,10 +686,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
@@ -702,216 +701,216 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="222" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="C2" s="5">
         <v>44808</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="C3" s="5">
         <v>44805</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C4" s="5">
         <v>44804</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="5">
         <v>44798</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5">
         <v>44790</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5">
         <v>44763</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" s="5">
         <v>43718</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
